--- a/output/pdf_financials_xlsx/SGRO.xlsx
+++ b/output/pdf_financials_xlsx/SGRO.xlsx
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>4.728197</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.728197</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.728197</v>
       </c>
     </row>
     <row r="93">
@@ -3041,7 +3041,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="n">
         <v>4.728197</v>
       </c>

--- a/output/pdf_financials_xlsx/SGRO.xlsx
+++ b/output/pdf_financials_xlsx/SGRO.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.003875</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.0008050000000000001</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000483</v>
       </c>
     </row>
     <row r="13">
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.375055</v>
+        <v>-0.37893</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.309158</v>
+        <v>0.308353</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.309158</v>
+        <v>0.308675</v>
       </c>
     </row>
     <row r="28">
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.375055</v>
+        <v>-0.37893</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.309158</v>
+        <v>0.308353</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.309158</v>
+        <v>0.308675</v>
       </c>
     </row>
     <row r="30">
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.877735</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.7826610000000001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.34874</v>
       </c>
     </row>
     <row r="35">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.877735</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.7826610000000001</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.1</v>
+        <v>0.44874</v>
       </c>
     </row>
     <row r="37">
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.877735</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.7826610000000001</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.373245</v>
+        <v>0.024505</v>
       </c>
     </row>
     <row r="49">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">

--- a/output/pdf_financials_xlsx/SGRO.xlsx
+++ b/output/pdf_financials_xlsx/SGRO.xlsx
@@ -1480,13 +1480,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.005623</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.02061</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.026999</v>
       </c>
     </row>
     <row r="65">
@@ -1544,13 +1544,13 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0.023623</v>
+        <v>0.029246</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.04887</v>
+        <v>0.06948</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.051359</v>
+        <v>0.078358</v>
       </c>
     </row>
     <row r="69">
@@ -2055,7 +2055,7 @@
         <v>0.309158</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.309158</v>
+        <v>-1.981436</v>
       </c>
     </row>
     <row r="100">
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="115">
@@ -3198,7 +3198,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
         <v>-0.375055</v>
       </c>
@@ -3477,7 +3481,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -3733,7 +3741,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
